--- a/data/trending_integrated_20261012_10.xlsx
+++ b/data/trending_integrated_20261012_10.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13980</v>
+        <v>13780</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+25.49%</t>
+          <t>'+23.70%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0.64</v>
       </c>
       <c r="E2" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="F2" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="G2" t="n">
-        <v>103</v>
+        <v>114</v>
       </c>
       <c r="H2" t="n">
         <v>1.01</v>
@@ -610,7 +610,7 @@
         <v>0.37</v>
       </c>
       <c r="O2" t="n">
-        <v>106083058650</v>
+        <v>115406775050</v>
       </c>
       <c r="P2" t="n">
         <v>19380</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>건설 사업 확정 및 2차 상승 기대감. 외국인+프로그램 매수세 동반.</t>
+          <t>건설주 상승 기대감 속 거래량 미미, 외국인/프매 장난질 의혹 제기.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['건설', '상승', '외국인']</t>
+          <t>['건설', '거래량', '외국인']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15420</v>
+        <v>15530</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+10.86%</t>
+          <t>'+11.65%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.12</v>
       </c>
       <c r="E3" t="n">
-        <v>87</v>
+        <v>112</v>
       </c>
       <c r="F3" t="n">
-        <v>42</v>
+        <v>58</v>
       </c>
       <c r="G3" t="n">
-        <v>103</v>
+        <v>131</v>
       </c>
       <c r="H3" t="n">
         <v>0.21</v>
@@ -693,7 +693,7 @@
         <v>13350</v>
       </c>
       <c r="L3" t="n">
-        <v>15440</v>
+        <v>15720</v>
       </c>
       <c r="M3" t="n">
         <v>13350</v>
@@ -702,7 +702,7 @@
         <v>0.09</v>
       </c>
       <c r="O3" t="n">
-        <v>46272588805</v>
+        <v>59876089615</v>
       </c>
       <c r="P3" t="n">
         <v>28700</v>
@@ -718,7 +718,7 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>방산주 테마 및 보호예수 해제 영향. 장기적 관점에서 접근 필요.</t>
+          <t>누리호 발사 성공 연관성 부각, 방산/우주 테마 기대감 반영.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['방산주', '보호예수', '장기투자']</t>
+          <t>['방산', '우주', '누리호']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16570</v>
+        <v>16480</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'-0.60%</t>
+          <t>'-1.14%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.01</v>
       </c>
       <c r="E4" t="n">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F4" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G4" t="n">
-        <v>240</v>
+        <v>266</v>
       </c>
       <c r="H4" t="n">
         <v>9.470000000000001</v>
@@ -794,7 +794,7 @@
         <v>9.460000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>19868417560</v>
+        <v>21760948220</v>
       </c>
       <c r="P4" t="n">
         <v>40350</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>대차 관련 논란과 소액주주연대 활동. 주가 상승에 대한 회의적인 시각.</t>
+          <t>주가 부양 및 범죄 척결 요구 주장 반복, 구체적 근거 제시 부족.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['대차', '소액주주', '주가']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -839,70 +839,70 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>삼기에너지솔루션즈</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2290</v>
+        <v>255500</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'-0.65%</t>
+          <t>'-2.48%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.16</v>
+        <v>-0.03</v>
       </c>
       <c r="E5" t="n">
-        <v>42</v>
+        <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>23</v>
+        <v>468</v>
       </c>
       <c r="G5" t="n">
-        <v>34</v>
+        <v>1886</v>
       </c>
       <c r="H5" t="n">
-        <v>1.48</v>
+        <v>46.35</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>2305</v>
+        <v>262000</v>
       </c>
       <c r="K5" t="n">
-        <v>2430</v>
+        <v>260000</v>
       </c>
       <c r="L5" t="n">
-        <v>2445</v>
+        <v>262500</v>
       </c>
       <c r="M5" t="n">
-        <v>2260</v>
+        <v>255000</v>
       </c>
       <c r="N5" t="n">
-        <v>1.32</v>
+        <v>46.38</v>
       </c>
       <c r="O5" t="n">
-        <v>23145833202</v>
+        <v>1116356371250</v>
       </c>
       <c r="P5" t="n">
-        <v>2465</v>
+        <v>374500</v>
       </c>
       <c r="Q5" t="n">
-        <v>865</v>
+        <v>90200</v>
       </c>
       <c r="R5" t="n">
-        <v>-316000</v>
+        <v>-171000</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>90000</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>인공지능 데이터센터 확대에 따른 ESS용 유연회로기판 매출 급증 기대.</t>
+          <t>반도체 업황 부진 우려 속, 로봇용 D램 수요 증가 뉴스 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
@@ -911,11 +911,11 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['ESS', '유연회로기판', '매출']</t>
+          <t>['반도체', 'D램', '수요']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,7 +924,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>419050</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>45050</v>
+        <v>44500</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-1.31%</t>
+          <t>'-2.52%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>-0.06</v>
       </c>
       <c r="E6" t="n">
-        <v>243</v>
+        <v>258</v>
       </c>
       <c r="F6" t="n">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="G6" t="n">
-        <v>1493</v>
+        <v>1564</v>
       </c>
       <c r="H6" t="n">
         <v>13.33</v>
@@ -972,13 +972,13 @@
         <v>47550</v>
       </c>
       <c r="M6" t="n">
-        <v>45000</v>
+        <v>44450</v>
       </c>
       <c r="N6" t="n">
         <v>13.39</v>
       </c>
       <c r="O6" t="n">
-        <v>19973946100</v>
+        <v>23382742975</v>
       </c>
       <c r="P6" t="n">
         <v>69200</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>HLB 간암 1차 치료제 리보세라닙 FDA 재승인 서류 제출. 연말 30만 기대.</t>
+          <t>HLB 간암 1차 치료제 FDA 재승인 서류 제출, 리보세라닙/캄렐리주맙 병용요법 기대감.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['리보세라닙', 'FDA', '재승인']</t>
+          <t>['FDA', '리보세라닙', '간암']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1023,70 +1023,70 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>삼기에너지솔루션즈</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>256500</v>
+        <v>2245</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-2.10%</t>
+          <t>'-2.60%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.03</v>
+        <v>0.16</v>
       </c>
       <c r="E7" t="n">
-        <v>776</v>
+        <v>46</v>
       </c>
       <c r="F7" t="n">
-        <v>451</v>
+        <v>23</v>
       </c>
       <c r="G7" t="n">
-        <v>2203</v>
+        <v>46</v>
       </c>
       <c r="H7" t="n">
-        <v>46.35</v>
+        <v>1.48</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>262000</v>
+        <v>2305</v>
       </c>
       <c r="K7" t="n">
-        <v>260000</v>
+        <v>2430</v>
       </c>
       <c r="L7" t="n">
-        <v>262500</v>
+        <v>2445</v>
       </c>
       <c r="M7" t="n">
-        <v>255000</v>
+        <v>2235</v>
       </c>
       <c r="N7" t="n">
-        <v>46.38</v>
+        <v>1.32</v>
       </c>
       <c r="O7" t="n">
-        <v>1035610912500</v>
+        <v>25050919407</v>
       </c>
       <c r="P7" t="n">
-        <v>374500</v>
+        <v>2465</v>
       </c>
       <c r="Q7" t="n">
-        <v>90200</v>
+        <v>865</v>
       </c>
       <c r="R7" t="n">
-        <v>-171000</v>
+        <v>-316000</v>
       </c>
       <c r="S7" t="n">
-        <v>90000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>반도체 주 상승 시작 전망. 마이크론 파업 및 로봇 D램 수요 증가 기대.</t>
+          <t>인공지능 데이터센터 확대에 따른 ESS 매출 증대 전망.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,11 +1095,11 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['반도체', 'D램', '로봇']</t>
+          <t>['ESS', '데이터센터', '매출']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>419050</t>
         </is>
       </c>
     </row>
@@ -1119,24 +1119,24 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18290</v>
+        <v>18260</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-3.02%</t>
+          <t>'-3.18%</t>
         </is>
       </c>
       <c r="D8" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E8" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F8" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="G8" t="n">
-        <v>179</v>
+        <v>201</v>
       </c>
       <c r="H8" t="n">
         <v>27.61</v>
@@ -1162,7 +1162,7 @@
         <v>27.68</v>
       </c>
       <c r="O8" t="n">
-        <v>16874853445</v>
+        <v>18243307850</v>
       </c>
       <c r="P8" t="n">
         <v>35350</v>
@@ -1178,16 +1178,16 @@
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>LNG·FLNG 수주 랠리에도 주가 하락. 조선업 투자 비관론.</t>
+          <t>조선주 순환매 기대감에도 주가 하락, LNG/FLNG 수주 소식 언급.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['LNG', 'FLNG', '조선업']</t>
+          <t>['조선', '수주', 'LNG']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7870</v>
+        <v>7880</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-3.55%</t>
+          <t>'-3.43%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.01</v>
       </c>
       <c r="E9" t="n">
-        <v>60</v>
+        <v>69</v>
       </c>
       <c r="F9" t="n">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G9" t="n">
-        <v>246</v>
+        <v>260</v>
       </c>
       <c r="H9" t="n">
         <v>26.37</v>
@@ -1254,7 +1254,7 @@
         <v>26.38</v>
       </c>
       <c r="O9" t="n">
-        <v>8204786620</v>
+        <v>9087062645</v>
       </c>
       <c r="P9" t="n">
         <v>17950</v>
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1620000</v>
+        <v>1614000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-3.63%</t>
+          <t>'-3.99%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>483</v>
+        <v>469</v>
       </c>
       <c r="G10" t="n">
-        <v>2288</v>
+        <v>1762</v>
       </c>
       <c r="H10" t="n">
         <v>49.52</v>
@@ -1340,13 +1340,13 @@
         <v>1653000</v>
       </c>
       <c r="M10" t="n">
-        <v>1615000</v>
+        <v>1611000</v>
       </c>
       <c r="N10" t="n">
         <v>49.59</v>
       </c>
       <c r="O10" t="n">
-        <v>1307554849000</v>
+        <v>1425174333500</v>
       </c>
       <c r="P10" t="n">
         <v>2987000</v>
@@ -1362,16 +1362,16 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>로봇용 D램 수요 증가 및 소부장 테마. 주가 하락 및 최태원 회장 발언 논란.</t>
+          <t>솔리다임 쪼개기 상장 관련 논란 및 오너 리스크 우려 제기.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['D램', '로봇', '소부장']</t>
+          <t>['오너 리스크', 'IPO', '솔리다임']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16050</v>
+        <v>15860</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-5.42%</t>
+          <t>'-6.54%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.6</v>
       </c>
       <c r="E11" t="n">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="F11" t="n">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="G11" t="n">
-        <v>280</v>
+        <v>293</v>
       </c>
       <c r="H11" t="n">
         <v>3.37</v>
@@ -1432,13 +1432,13 @@
         <v>17400</v>
       </c>
       <c r="M11" t="n">
-        <v>16030</v>
+        <v>15850</v>
       </c>
       <c r="N11" t="n">
         <v>3.97</v>
       </c>
       <c r="O11" t="n">
-        <v>38699794980</v>
+        <v>46110720705</v>
       </c>
       <c r="P11" t="n">
         <v>31500</v>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>AI 및 광통신 시장 성장률에 따른 주가 상승 기대. 미국 광통신 대장주 신고가.</t>
+          <t>AI 광통신 시장 성장 기대감, 미국 광통신 대장주 신고가 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>

--- a/data/trending_integrated_20261012_10.xlsx
+++ b/data/trending_integrated_20261012_10.xlsx
@@ -567,24 +567,24 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13780</v>
+        <v>13730</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+23.70%</t>
+          <t>'+23.25%</t>
         </is>
       </c>
       <c r="D2" t="n">
         <v>0.64</v>
       </c>
       <c r="E2" t="n">
-        <v>52</v>
+        <v>56</v>
       </c>
       <c r="F2" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="G2" t="n">
-        <v>114</v>
+        <v>129</v>
       </c>
       <c r="H2" t="n">
         <v>1.01</v>
@@ -610,7 +610,7 @@
         <v>0.37</v>
       </c>
       <c r="O2" t="n">
-        <v>115406775050</v>
+        <v>122982123765</v>
       </c>
       <c r="P2" t="n">
         <v>19380</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>건설주 상승 기대감 속 거래량 미미, 외국인/프매 장난질 의혹 제기.</t>
+          <t>특허 출원 및 건설 확정 기반의 2차 상승 기대감. 다만, 거래량 부족과 만원대 회복 여부에 대한 관망세.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['건설', '거래량', '외국인']</t>
+          <t>['특허 출원', '건설 확정', '거래량']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -659,24 +659,24 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15530</v>
+        <v>15120</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+11.65%</t>
+          <t>'+8.70%</t>
         </is>
       </c>
       <c r="D3" t="n">
         <v>0.12</v>
       </c>
       <c r="E3" t="n">
-        <v>112</v>
+        <v>125</v>
       </c>
       <c r="F3" t="n">
-        <v>58</v>
+        <v>64</v>
       </c>
       <c r="G3" t="n">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="H3" t="n">
         <v>0.21</v>
@@ -702,7 +702,7 @@
         <v>0.09</v>
       </c>
       <c r="O3" t="n">
-        <v>59876089615</v>
+        <v>68311528640</v>
       </c>
       <c r="P3" t="n">
         <v>28700</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>누리호 발사 성공 연관성 부각, 방산/우주 테마 기대감 반영.</t>
+          <t>핵심 장비 탑재한 누리호 발사 성공 및 우주 테마 기대감. 보호예수 해제에 대한 관망세.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['방산', '우주', '누리호']</t>
+          <t>['누리호', '우주 테마', '보호예수']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16480</v>
+        <v>16440</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'-1.14%</t>
+          <t>'-1.38%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.01</v>
       </c>
       <c r="E4" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="F4" t="n">
         <v>37</v>
       </c>
       <c r="G4" t="n">
-        <v>266</v>
+        <v>282</v>
       </c>
       <c r="H4" t="n">
         <v>9.470000000000001</v>
@@ -794,7 +794,7 @@
         <v>9.460000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>21760948220</v>
+        <v>24196724845</v>
       </c>
       <c r="P4" t="n">
         <v>40350</v>
@@ -810,7 +810,7 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>주가 부양 및 범죄 척결 요구 주장 반복, 구체적 근거 제시 부족.</t>
+          <t>소액주주연대의 적극적인 활동과 범죄 척결 주장. 3만원대 회복에 대한 희망.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['소액주주연대', '범죄 척결', '3만원']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -857,10 +857,10 @@
         <v>800</v>
       </c>
       <c r="F5" t="n">
-        <v>468</v>
+        <v>475</v>
       </c>
       <c r="G5" t="n">
-        <v>1886</v>
+        <v>1620</v>
       </c>
       <c r="H5" t="n">
         <v>46.35</v>
@@ -886,7 +886,7 @@
         <v>46.38</v>
       </c>
       <c r="O5" t="n">
-        <v>1116356371250</v>
+        <v>1210912051000</v>
       </c>
       <c r="P5" t="n">
         <v>374500</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>반도체 업황 부진 우려 속, 로봇용 D램 수요 증가 뉴스 언급.</t>
+          <t>역대급 실적 기대에도 불구하고 주가 하락 지속. 정치적 이슈와 노조 관련 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['반도체', 'D램', '수요']</t>
+          <t>['실적', '정치', '노조']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -931,31 +931,31 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>삼기에너지솔루션즈</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>44500</v>
+        <v>2235</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-2.52%</t>
+          <t>'-3.04%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.06</v>
+        <v>0.16</v>
       </c>
       <c r="E6" t="n">
-        <v>258</v>
+        <v>50</v>
       </c>
       <c r="F6" t="n">
-        <v>172</v>
+        <v>25</v>
       </c>
       <c r="G6" t="n">
-        <v>1564</v>
+        <v>55</v>
       </c>
       <c r="H6" t="n">
-        <v>13.33</v>
+        <v>1.48</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,51 +963,51 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>45650</v>
+        <v>2305</v>
       </c>
       <c r="K6" t="n">
-        <v>47550</v>
+        <v>2430</v>
       </c>
       <c r="L6" t="n">
-        <v>47550</v>
+        <v>2445</v>
       </c>
       <c r="M6" t="n">
-        <v>44450</v>
+        <v>2225</v>
       </c>
       <c r="N6" t="n">
-        <v>13.39</v>
+        <v>1.32</v>
       </c>
       <c r="O6" t="n">
-        <v>23382742975</v>
+        <v>26071198037</v>
       </c>
       <c r="P6" t="n">
-        <v>69200</v>
+        <v>2465</v>
       </c>
       <c r="Q6" t="n">
-        <v>24150</v>
+        <v>865</v>
       </c>
       <c r="R6" t="n">
-        <v>-128000</v>
+        <v>-316000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>HLB 간암 1차 치료제 FDA 재승인 서류 제출, 리보세라닙/캄렐리주맙 병용요법 기대감.</t>
+          <t>AI 데이터센터 확대에 따른 에너지 저장장치용 유연회로기판 매출 급증 전망. 주가 상승에 대한 기대감.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.5</v>
+        <v>0.3</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['FDA', '리보세라닙', '간암']</t>
+          <t>['AI', 'ESS', '유연회로기판']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,77 +1016,77 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>419050</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼기에너지솔루션즈</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>2245</v>
+        <v>18230</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-2.60%</t>
+          <t>'-3.34%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.16</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="F7" t="n">
-        <v>23</v>
+        <v>45</v>
       </c>
       <c r="G7" t="n">
-        <v>46</v>
+        <v>209</v>
       </c>
       <c r="H7" t="n">
-        <v>1.48</v>
+        <v>27.61</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>2305</v>
+        <v>18860</v>
       </c>
       <c r="K7" t="n">
-        <v>2430</v>
+        <v>18690</v>
       </c>
       <c r="L7" t="n">
-        <v>2445</v>
+        <v>18760</v>
       </c>
       <c r="M7" t="n">
-        <v>2235</v>
+        <v>18220</v>
       </c>
       <c r="N7" t="n">
-        <v>1.32</v>
+        <v>27.68</v>
       </c>
       <c r="O7" t="n">
-        <v>25050919407</v>
+        <v>19778439750</v>
       </c>
       <c r="P7" t="n">
-        <v>2465</v>
+        <v>35350</v>
       </c>
       <c r="Q7" t="n">
-        <v>865</v>
+        <v>18220</v>
       </c>
       <c r="R7" t="n">
-        <v>-316000</v>
+        <v>25000</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>11000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>인공지능 데이터센터 확대에 따른 ESS 매출 증대 전망.</t>
+          <t>LNG·FLNG 수주 랠리에도 불구하고 주가 급락. 타 조선주 대비 부진 및 신저점 갱신.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,11 +1095,11 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['ESS', '데이터센터', '매출']</t>
+          <t>['수주 랠리', '조선주', '신저점']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,90 +1108,90 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>419050</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18260</v>
+        <v>44100</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-3.18%</t>
+          <t>'-3.40%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="E8" t="n">
-        <v>72</v>
+        <v>280</v>
       </c>
       <c r="F8" t="n">
-        <v>44</v>
+        <v>184</v>
       </c>
       <c r="G8" t="n">
-        <v>201</v>
+        <v>1625</v>
       </c>
       <c r="H8" t="n">
-        <v>27.61</v>
+        <v>13.33</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>18860</v>
+        <v>45650</v>
       </c>
       <c r="K8" t="n">
-        <v>18690</v>
+        <v>47550</v>
       </c>
       <c r="L8" t="n">
-        <v>18760</v>
+        <v>47550</v>
       </c>
       <c r="M8" t="n">
-        <v>18260</v>
+        <v>43900</v>
       </c>
       <c r="N8" t="n">
-        <v>27.68</v>
+        <v>13.39</v>
       </c>
       <c r="O8" t="n">
-        <v>18243307850</v>
+        <v>26028562775</v>
       </c>
       <c r="P8" t="n">
-        <v>35350</v>
+        <v>69200</v>
       </c>
       <c r="Q8" t="n">
-        <v>18260</v>
+        <v>24150</v>
       </c>
       <c r="R8" t="n">
-        <v>25000</v>
+        <v>-128000</v>
       </c>
       <c r="S8" t="n">
-        <v>11000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>조선주 순환매 기대감에도 주가 하락, LNG/FLNG 수주 소식 언급.</t>
+          <t>HLB 간암 1차 치료제 FDA 재승인 서류 제출, 리보세라닙/캄렐리주맙 병용요법 기대감.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['조선', '수주', 'LNG']</t>
+          <t>['FDA', '리보세라닙', '간암']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
@@ -1211,24 +1211,24 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7880</v>
+        <v>7870</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-3.43%</t>
+          <t>'-3.55%</t>
         </is>
       </c>
       <c r="D9" t="n">
         <v>-0.01</v>
       </c>
       <c r="E9" t="n">
-        <v>69</v>
+        <v>75</v>
       </c>
       <c r="F9" t="n">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G9" t="n">
-        <v>260</v>
+        <v>297</v>
       </c>
       <c r="H9" t="n">
         <v>26.37</v>
@@ -1248,19 +1248,19 @@
         <v>8110</v>
       </c>
       <c r="M9" t="n">
-        <v>7870</v>
+        <v>7860</v>
       </c>
       <c r="N9" t="n">
         <v>26.38</v>
       </c>
       <c r="O9" t="n">
-        <v>9087062645</v>
+        <v>9630043480</v>
       </c>
       <c r="P9" t="n">
         <v>17950</v>
       </c>
       <c r="Q9" t="n">
-        <v>7870</v>
+        <v>7860</v>
       </c>
       <c r="R9" t="n">
         <v>-299000</v>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>미래 전망 없는 사업으로 투자 대상 아님. 주가 하락 및 상폐 우려.</t>
+          <t>신규 기술(FLiPP) 관련 뉴스에도 불구하고 주가 하락 지속. 유상증자 및 상폐 가능성에 대한 우려.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
@@ -1279,7 +1279,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['미래전망', '주가하락', '상폐']</t>
+          <t>['FLiPP', '유상증자', '상폐']</t>
         </is>
       </c>
       <c r="X9" t="n">
@@ -1303,11 +1303,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1614000</v>
+        <v>1611000</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-3.99%</t>
+          <t>'-4.16%</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -1317,10 +1317,10 @@
         <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="G10" t="n">
-        <v>1762</v>
+        <v>1702</v>
       </c>
       <c r="H10" t="n">
         <v>49.52</v>
@@ -1340,13 +1340,13 @@
         <v>1653000</v>
       </c>
       <c r="M10" t="n">
-        <v>1611000</v>
+        <v>1610000</v>
       </c>
       <c r="N10" t="n">
         <v>49.59</v>
       </c>
       <c r="O10" t="n">
-        <v>1425174333500</v>
+        <v>1517568030500</v>
       </c>
       <c r="P10" t="n">
         <v>2987000</v>
@@ -1362,7 +1362,7 @@
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>솔리다임 쪼개기 상장 관련 논란 및 오너 리스크 우려 제기.</t>
+          <t>정치적 이슈 및 오너 리스크로 인한 주가 급락. 솔리다임 IPO 관련 논란.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
@@ -1371,7 +1371,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['오너 리스크', 'IPO', '솔리다임']</t>
+          <t>['정치', '오너 리스크', '솔리다임 IPO']</t>
         </is>
       </c>
       <c r="X10" t="n">
@@ -1395,24 +1395,24 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15860</v>
+        <v>15800</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-6.54%</t>
+          <t>'-6.89%</t>
         </is>
       </c>
       <c r="D11" t="n">
         <v>-0.6</v>
       </c>
       <c r="E11" t="n">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="F11" t="n">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="G11" t="n">
-        <v>293</v>
+        <v>319</v>
       </c>
       <c r="H11" t="n">
         <v>3.37</v>
@@ -1432,13 +1432,13 @@
         <v>17400</v>
       </c>
       <c r="M11" t="n">
-        <v>15850</v>
+        <v>15800</v>
       </c>
       <c r="N11" t="n">
         <v>3.97</v>
       </c>
       <c r="O11" t="n">
-        <v>46110720705</v>
+        <v>50649164560</v>
       </c>
       <c r="P11" t="n">
         <v>31500</v>
@@ -1454,16 +1454,16 @@
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>AI 광통신 시장 성장 기대감, 미국 광통신 대장주 신고가 언급.</t>
+          <t>광통신 대세 테마 속에서 주가 하락 지속. 공매도 규제 및 지지선 이탈에 대한 우려.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['광통신', 'AI', '성장률']</t>
+          <t>['광통신', '공매도', '지지선']</t>
         </is>
       </c>
       <c r="X11" t="n">

--- a/data/trending_integrated_20261012_10.xlsx
+++ b/data/trending_integrated_20261012_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z11"/>
+  <dimension ref="A1:Z15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -563,79 +563,79 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>서산</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13730</v>
+        <v>6760</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>'+23.25%</t>
+          <t>'+30.00%</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.64</v>
+        <v>0.61</v>
       </c>
       <c r="E2" t="n">
-        <v>56</v>
+        <v>40</v>
       </c>
       <c r="F2" t="n">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="G2" t="n">
-        <v>129</v>
+        <v>107</v>
       </c>
       <c r="H2" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J2" t="n">
-        <v>11140</v>
+        <v>5200</v>
       </c>
       <c r="K2" t="n">
-        <v>12000</v>
+        <v>5910</v>
       </c>
       <c r="L2" t="n">
-        <v>14100</v>
+        <v>6760</v>
       </c>
       <c r="M2" t="n">
-        <v>11710</v>
+        <v>5790</v>
       </c>
       <c r="N2" t="n">
-        <v>0.37</v>
+        <v>0.66</v>
       </c>
       <c r="O2" t="n">
-        <v>122982123765</v>
+        <v>19633786500</v>
       </c>
       <c r="P2" t="n">
-        <v>19380</v>
+        <v>10300</v>
       </c>
       <c r="Q2" t="n">
-        <v>3200</v>
+        <v>952</v>
       </c>
       <c r="R2" t="n">
-        <v>-414000</v>
+        <v>31000</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>특허 출원 및 건설 확정 기반의 2차 상승 기대감. 다만, 거래량 부족과 만원대 회복 여부에 대한 관망세.</t>
+          <t>대장주로서 텐버거 확정 및 PHC파일 관련 수혜 기대감. 800조 사업 시작점 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['특허 출원', '건설 확정', '거래량']</t>
+          <t>['PHC파일', '대장주', '수혜주']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -648,77 +648,77 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>079650</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>덕산넵코어스</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15120</v>
+        <v>13850</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+8.70%</t>
+          <t>'+24.33%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.12</v>
+        <v>0.64</v>
       </c>
       <c r="E3" t="n">
-        <v>125</v>
+        <v>59</v>
       </c>
       <c r="F3" t="n">
-        <v>64</v>
+        <v>42</v>
       </c>
       <c r="G3" t="n">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="H3" t="n">
-        <v>0.21</v>
+        <v>1.01</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J3" t="n">
-        <v>13910</v>
+        <v>11140</v>
       </c>
       <c r="K3" t="n">
-        <v>13350</v>
+        <v>12000</v>
       </c>
       <c r="L3" t="n">
-        <v>15720</v>
+        <v>14100</v>
       </c>
       <c r="M3" t="n">
-        <v>13350</v>
+        <v>11710</v>
       </c>
       <c r="N3" t="n">
-        <v>0.09</v>
+        <v>0.37</v>
       </c>
       <c r="O3" t="n">
-        <v>68311528640</v>
+        <v>127216491200</v>
       </c>
       <c r="P3" t="n">
-        <v>28700</v>
+        <v>19380</v>
       </c>
       <c r="Q3" t="n">
-        <v>11600</v>
+        <v>3200</v>
       </c>
       <c r="R3" t="n">
-        <v>85000</v>
+        <v>-414000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>핵심 장비 탑재한 누리호 발사 성공 및 우주 테마 기대감. 보호예수 해제에 대한 관망세.</t>
+          <t>금호건설, 자체 개발 특허 출원 및 건설 확정으로 2차 상승 기대. 거래량 부진은 아쉬움.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,11 +727,11 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['누리호', '우주 테마', '보호예수']</t>
+          <t>['특허 출원', '건설 확정', '2차 상승']</t>
         </is>
       </c>
       <c r="X3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
@@ -740,90 +740,90 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>266690</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16440</v>
+        <v>1649</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'-1.38%</t>
+          <t>'+18.89%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.01</v>
+        <v>0.36</v>
       </c>
       <c r="E4" t="n">
-        <v>65</v>
+        <v>40</v>
       </c>
       <c r="F4" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="G4" t="n">
-        <v>282</v>
+        <v>82</v>
       </c>
       <c r="H4" t="n">
-        <v>9.470000000000001</v>
+        <v>1.26</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>16670</v>
+        <v>1387</v>
       </c>
       <c r="K4" t="n">
-        <v>16500</v>
+        <v>1450</v>
       </c>
       <c r="L4" t="n">
-        <v>16870</v>
+        <v>1710</v>
       </c>
       <c r="M4" t="n">
-        <v>16420</v>
+        <v>1436</v>
       </c>
       <c r="N4" t="n">
-        <v>9.460000000000001</v>
+        <v>0.9</v>
       </c>
       <c r="O4" t="n">
-        <v>24196724845</v>
+        <v>8966943630</v>
       </c>
       <c r="P4" t="n">
-        <v>40350</v>
+        <v>2930</v>
       </c>
       <c r="Q4" t="n">
-        <v>3320</v>
+        <v>910</v>
       </c>
       <c r="R4" t="n">
-        <v>221000</v>
+        <v>-108000</v>
       </c>
       <c r="S4" t="n">
-        <v>11000</v>
+        <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>소액주주연대의 적극적인 활동과 범죄 척결 주장. 3만원대 회복에 대한 희망.</t>
+          <t>강동씨앤엘, 시멘트 수요 폭발 기대감 속 외국인 및 기관 매수세 유입. 대장주 역할 기대.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.3</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['소액주주연대', '범죄 척결', '3만원']</t>
+          <t>['시멘트 수요', '외국인 매수', '대장주']</t>
         </is>
       </c>
       <c r="X4" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -832,90 +832,90 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>198440</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>덕산넵코어스</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>255500</v>
+        <v>15230</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'-2.48%</t>
+          <t>'+9.49%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>-0.03</v>
+        <v>0.12</v>
       </c>
       <c r="E5" t="n">
-        <v>800</v>
+        <v>136</v>
       </c>
       <c r="F5" t="n">
-        <v>475</v>
+        <v>65</v>
       </c>
       <c r="G5" t="n">
-        <v>1620</v>
+        <v>149</v>
       </c>
       <c r="H5" t="n">
-        <v>46.35</v>
+        <v>0.21</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>262000</v>
+        <v>13910</v>
       </c>
       <c r="K5" t="n">
-        <v>260000</v>
+        <v>13350</v>
       </c>
       <c r="L5" t="n">
-        <v>262500</v>
+        <v>15790</v>
       </c>
       <c r="M5" t="n">
-        <v>255000</v>
+        <v>13350</v>
       </c>
       <c r="N5" t="n">
-        <v>46.38</v>
+        <v>0.09</v>
       </c>
       <c r="O5" t="n">
-        <v>1210912051000</v>
+        <v>79000055465</v>
       </c>
       <c r="P5" t="n">
-        <v>374500</v>
+        <v>28700</v>
       </c>
       <c r="Q5" t="n">
-        <v>90200</v>
+        <v>11600</v>
       </c>
       <c r="R5" t="n">
-        <v>-171000</v>
+        <v>85000</v>
       </c>
       <c r="S5" t="n">
-        <v>90000</v>
+        <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>역대급 실적 기대에도 불구하고 주가 하락 지속. 정치적 이슈와 노조 관련 언급.</t>
+          <t>덕산넵코어스, 미국 방산주 팔란티어 상승에 따른 기대감. 상한가 및 17000원 돌파 기대.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['실적', '정치', '노조']</t>
+          <t>['방산주', '팔란티어', '상한가']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>266690</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>삼기에너지솔루션즈</t>
+          <t>삼표시멘트</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2235</v>
+        <v>7350</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'-3.04%</t>
+          <t>'+3.81%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.16</v>
+        <v>-1.1</v>
       </c>
       <c r="E6" t="n">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="F6" t="n">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="G6" t="n">
-        <v>55</v>
+        <v>144</v>
       </c>
       <c r="H6" t="n">
-        <v>1.48</v>
+        <v>1.99</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,38 +963,38 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>2305</v>
+        <v>7080</v>
       </c>
       <c r="K6" t="n">
-        <v>2430</v>
+        <v>6830</v>
       </c>
       <c r="L6" t="n">
-        <v>2445</v>
+        <v>7530</v>
       </c>
       <c r="M6" t="n">
-        <v>2225</v>
+        <v>6720</v>
       </c>
       <c r="N6" t="n">
-        <v>1.32</v>
+        <v>3.09</v>
       </c>
       <c r="O6" t="n">
-        <v>26071198037</v>
+        <v>29889724740</v>
       </c>
       <c r="P6" t="n">
-        <v>2465</v>
+        <v>23500</v>
       </c>
       <c r="Q6" t="n">
-        <v>865</v>
+        <v>2890</v>
       </c>
       <c r="R6" t="n">
-        <v>-316000</v>
+        <v>44000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>AI 데이터센터 확대에 따른 에너지 저장장치용 유연회로기판 매출 급증 전망. 주가 상승에 대한 기대감.</t>
+          <t>삼표시멘트, 성수 메가프로젝트 및 건설 기초 소재 대장주로서의 입지 부각. 외국인 매수 증가 및 상가 기대.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,11 +1003,11 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['AI', 'ESS', '유연회로기판']</t>
+          <t>['성수 메가프로젝트', '건설 기초 소재', '외국인 매수']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,38 +1016,38 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>419050</t>
+          <t>038500</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18230</v>
+        <v>16370</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-3.34%</t>
+          <t>'-1.80%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="E7" t="n">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="F7" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G7" t="n">
-        <v>209</v>
+        <v>300</v>
       </c>
       <c r="H7" t="n">
-        <v>27.61</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -1055,51 +1055,51 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>18860</v>
+        <v>16670</v>
       </c>
       <c r="K7" t="n">
-        <v>18690</v>
+        <v>16500</v>
       </c>
       <c r="L7" t="n">
-        <v>18760</v>
+        <v>16870</v>
       </c>
       <c r="M7" t="n">
-        <v>18220</v>
+        <v>16240</v>
       </c>
       <c r="N7" t="n">
-        <v>27.68</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="O7" t="n">
-        <v>19778439750</v>
+        <v>26939989870</v>
       </c>
       <c r="P7" t="n">
-        <v>35350</v>
+        <v>40350</v>
       </c>
       <c r="Q7" t="n">
-        <v>18220</v>
+        <v>3320</v>
       </c>
       <c r="R7" t="n">
-        <v>25000</v>
+        <v>221000</v>
       </c>
       <c r="S7" t="n">
         <v>11000</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>LNG·FLNG 수주 랠리에도 불구하고 주가 급락. 타 조선주 대비 부진 및 신저점 갱신.</t>
+          <t>대우건설, 주주들의 적극적인 행동 촉구 및 범죄 척결 주장. 대차 해지, 뱅크런 관련 언급.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['수주 랠리', '조선주', '신저점']</t>
+          <t>['소액주주연대', '범죄 척결', '대차 해지']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,90 +1108,90 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>44100</v>
+        <v>255750</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-3.40%</t>
+          <t>'-2.39%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.06</v>
+        <v>-0.03</v>
       </c>
       <c r="E8" t="n">
-        <v>280</v>
+        <v>800</v>
       </c>
       <c r="F8" t="n">
-        <v>184</v>
+        <v>484</v>
       </c>
       <c r="G8" t="n">
-        <v>1625</v>
+        <v>1502</v>
       </c>
       <c r="H8" t="n">
-        <v>13.33</v>
+        <v>46.35</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>45650</v>
+        <v>262000</v>
       </c>
       <c r="K8" t="n">
-        <v>47550</v>
+        <v>260000</v>
       </c>
       <c r="L8" t="n">
-        <v>47550</v>
+        <v>262500</v>
       </c>
       <c r="M8" t="n">
-        <v>43900</v>
+        <v>254000</v>
       </c>
       <c r="N8" t="n">
-        <v>13.39</v>
+        <v>46.38</v>
       </c>
       <c r="O8" t="n">
-        <v>26028562775</v>
+        <v>1351407489500</v>
       </c>
       <c r="P8" t="n">
-        <v>69200</v>
+        <v>374500</v>
       </c>
       <c r="Q8" t="n">
-        <v>24150</v>
+        <v>90200</v>
       </c>
       <c r="R8" t="n">
-        <v>-128000</v>
+        <v>-171000</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>90000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>HLB 간암 1차 치료제 FDA 재승인 서류 제출, 리보세라닙/캄렐리주맙 병용요법 기대감.</t>
+          <t>삼성전자, 역대급 실적 발표 기대에도 불구하고 주가 하락세 지속. 국내 증시 및 정치 상황에 대한 불만 고조.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['FDA', '리보세라닙', '간암']</t>
+          <t>['역대급 실적', '국내 증시', '주가 하락']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,90 +1200,90 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7870</v>
+        <v>44450</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-3.55%</t>
+          <t>'-2.63%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.01</v>
+        <v>-0.06</v>
       </c>
       <c r="E9" t="n">
-        <v>75</v>
+        <v>298</v>
       </c>
       <c r="F9" t="n">
-        <v>53</v>
+        <v>193</v>
       </c>
       <c r="G9" t="n">
-        <v>297</v>
+        <v>1680</v>
       </c>
       <c r="H9" t="n">
-        <v>26.37</v>
+        <v>13.33</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>8160</v>
+        <v>45650</v>
       </c>
       <c r="K9" t="n">
-        <v>8070</v>
+        <v>47550</v>
       </c>
       <c r="L9" t="n">
-        <v>8110</v>
+        <v>47550</v>
       </c>
       <c r="M9" t="n">
-        <v>7860</v>
+        <v>43900</v>
       </c>
       <c r="N9" t="n">
-        <v>26.38</v>
+        <v>13.39</v>
       </c>
       <c r="O9" t="n">
-        <v>9630043480</v>
+        <v>27148532850</v>
       </c>
       <c r="P9" t="n">
-        <v>17950</v>
+        <v>69200</v>
       </c>
       <c r="Q9" t="n">
-        <v>7860</v>
+        <v>24150</v>
       </c>
       <c r="R9" t="n">
-        <v>-299000</v>
+        <v>-128000</v>
       </c>
       <c r="S9" t="n">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>신규 기술(FLiPP) 관련 뉴스에도 불구하고 주가 하락 지속. 유상증자 및 상폐 가능성에 대한 우려.</t>
+          <t>HLB 간암 1차 치료제 FDA 재승인 서류 제출, 리보세라닙/캄렐리주맙 병용요법 기대감.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['FLiPP', '유상증자', '상폐']</t>
+          <t>['FDA', '리보세라닙', '간암']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,90 +1292,90 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼기에너지솔루션즈</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1611000</v>
+        <v>2240</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-4.16%</t>
+          <t>'-2.82%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="E10" t="n">
-        <v>800</v>
+        <v>55</v>
       </c>
       <c r="F10" t="n">
-        <v>477</v>
+        <v>27</v>
       </c>
       <c r="G10" t="n">
-        <v>1702</v>
+        <v>58</v>
       </c>
       <c r="H10" t="n">
-        <v>49.52</v>
+        <v>1.48</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1681000</v>
+        <v>2305</v>
       </c>
       <c r="K10" t="n">
-        <v>1640000</v>
+        <v>2430</v>
       </c>
       <c r="L10" t="n">
-        <v>1653000</v>
+        <v>2445</v>
       </c>
       <c r="M10" t="n">
-        <v>1610000</v>
+        <v>2210</v>
       </c>
       <c r="N10" t="n">
-        <v>49.59</v>
+        <v>1.32</v>
       </c>
       <c r="O10" t="n">
-        <v>1517568030500</v>
+        <v>26947652411</v>
       </c>
       <c r="P10" t="n">
-        <v>2987000</v>
+        <v>2465</v>
       </c>
       <c r="Q10" t="n">
-        <v>403000</v>
+        <v>865</v>
       </c>
       <c r="R10" t="n">
-        <v>-217000</v>
+        <v>-316000</v>
       </c>
       <c r="S10" t="n">
-        <v>44000</v>
+        <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>정치적 이슈 및 오너 리스크로 인한 주가 급락. 솔리다임 IPO 관련 논란.</t>
+          <t>삼기에너지솔루션즈, AI 데이터센터 확대에 따른 에너지 저장 장치 매출 급증 기대. 주가 상승 가능성 언급.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['정치', '오너 리스크', '솔리다임 IPO']</t>
+          <t>['AI 데이터센터', '에너지 저장 장치', '매출 급증']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,97 +1384,465 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>419050</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15800</v>
+        <v>7890</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-6.89%</t>
+          <t>'-3.31%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.6</v>
+        <v>-0.01</v>
       </c>
       <c r="E11" t="n">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="F11" t="n">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="G11" t="n">
-        <v>319</v>
+        <v>351</v>
       </c>
       <c r="H11" t="n">
-        <v>3.37</v>
+        <v>26.37</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>16970</v>
+        <v>8160</v>
       </c>
       <c r="K11" t="n">
-        <v>17030</v>
+        <v>8070</v>
       </c>
       <c r="L11" t="n">
-        <v>17400</v>
+        <v>8110</v>
       </c>
       <c r="M11" t="n">
-        <v>15800</v>
+        <v>7850</v>
       </c>
       <c r="N11" t="n">
-        <v>3.97</v>
+        <v>26.38</v>
       </c>
       <c r="O11" t="n">
-        <v>50649164560</v>
+        <v>10128110160</v>
       </c>
       <c r="P11" t="n">
-        <v>31500</v>
+        <v>17950</v>
       </c>
       <c r="Q11" t="n">
-        <v>1272</v>
+        <v>7850</v>
       </c>
       <c r="R11" t="n">
-        <v>-29000</v>
+        <v>-299000</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>-2000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>광통신 대세 테마 속에서 주가 하락 지속. 공매도 규제 및 지지선 이탈에 대한 우려.</t>
+          <t>LG디스플레이, 신기술(Flip)에 대한 회의적인 시각과 유상증자 가능성 제기. 주가 하락 및 폐악질이라는 비판.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>['Flip 기술', '유상증자', '주가 하락']</t>
+        </is>
+      </c>
+      <c r="X11" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>034220</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>1621000</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>'-3.57%</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="E12" t="n">
+        <v>800</v>
+      </c>
+      <c r="F12" t="n">
+        <v>481</v>
+      </c>
+      <c r="G12" t="n">
+        <v>1728</v>
+      </c>
+      <c r="H12" t="n">
+        <v>49.52</v>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J12" t="n">
+        <v>1681000</v>
+      </c>
+      <c r="K12" t="n">
+        <v>1640000</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1653000</v>
+      </c>
+      <c r="M12" t="n">
+        <v>1605000</v>
+      </c>
+      <c r="N12" t="n">
+        <v>49.59</v>
+      </c>
+      <c r="O12" t="n">
+        <v>1629287966500</v>
+      </c>
+      <c r="P12" t="n">
+        <v>2987000</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>403000</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-217000</v>
+      </c>
+      <c r="S12" t="n">
+        <v>44000</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>정치적 이슈와 연계된 주가 하락 우려 및 배임 논란 제기. 최태원 회장 언급.</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>['정치', '배임', '주가방어']</t>
+        </is>
+      </c>
+      <c r="X12" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>000660</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>삼성중공업</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>18180</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>'-3.61%</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>-0.07000000000000001</v>
+      </c>
+      <c r="E13" t="n">
+        <v>81</v>
+      </c>
+      <c r="F13" t="n">
+        <v>47</v>
+      </c>
+      <c r="G13" t="n">
+        <v>223</v>
+      </c>
+      <c r="H13" t="n">
+        <v>27.61</v>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J13" t="n">
+        <v>18860</v>
+      </c>
+      <c r="K13" t="n">
+        <v>18690</v>
+      </c>
+      <c r="L13" t="n">
+        <v>18760</v>
+      </c>
+      <c r="M13" t="n">
+        <v>18100</v>
+      </c>
+      <c r="N13" t="n">
+        <v>27.68</v>
+      </c>
+      <c r="O13" t="n">
+        <v>22834299415</v>
+      </c>
+      <c r="P13" t="n">
+        <v>35350</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>18100</v>
+      </c>
+      <c r="R13" t="n">
+        <v>25000</v>
+      </c>
+      <c r="S13" t="n">
+        <v>11000</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>삼성중공업, LNG·FLNG 쌍끌이 수주 랠리에도 불구하고 주가 하락. 공매도 및 노조 문제 거론, 바닥 확인 필요.</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>['LNG 수주', 'FLNG 수주', '공매도']</t>
+        </is>
+      </c>
+      <c r="X13" t="n">
+        <v>6</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>010140</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>대한전선</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>26250</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>'-6.58%</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="E14" t="n">
+        <v>41</v>
+      </c>
+      <c r="F14" t="n">
+        <v>30</v>
+      </c>
+      <c r="G14" t="n">
+        <v>42</v>
+      </c>
+      <c r="H14" t="n">
+        <v>9.460000000000001</v>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J14" t="n">
+        <v>28100</v>
+      </c>
+      <c r="K14" t="n">
+        <v>27600</v>
+      </c>
+      <c r="L14" t="n">
+        <v>27800</v>
+      </c>
+      <c r="M14" t="n">
+        <v>26050</v>
+      </c>
+      <c r="N14" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="O14" t="n">
+        <v>32423993125</v>
+      </c>
+      <c r="P14" t="n">
+        <v>75900</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>15960</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-24000</v>
+      </c>
+      <c r="S14" t="n">
+        <v>2000</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>대한전선, 경영진 비판 및 실적 부진에 대한 실망감 표출. 하한가 예상 및 잡주라는 부정적 평가.</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>['경영진 비판', '실적 부진', '하한가']</t>
+        </is>
+      </c>
+      <c r="X14" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>001440</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>대한광통신</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>15840</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>'-6.66%</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="E15" t="n">
+        <v>102</v>
+      </c>
+      <c r="F15" t="n">
+        <v>54</v>
+      </c>
+      <c r="G15" t="n">
+        <v>341</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J15" t="n">
+        <v>16970</v>
+      </c>
+      <c r="K15" t="n">
+        <v>17030</v>
+      </c>
+      <c r="L15" t="n">
+        <v>17400</v>
+      </c>
+      <c r="M15" t="n">
+        <v>15650</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="O15" t="n">
+        <v>54752297030</v>
+      </c>
+      <c r="P15" t="n">
+        <v>31500</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>1272</v>
+      </c>
+      <c r="R15" t="n">
+        <v>-29000</v>
+      </c>
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>AI 관련 광통신 테마 상승 기대감과 공매도 규제 및 지수 하락 이슈 혼재. 10월 3만원 예상.</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="n">
         <v>0.2</v>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>['광통신', '공매도', '지지선']</t>
-        </is>
-      </c>
-      <c r="X11" t="n">
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>['광통신', 'AI', '테마']</t>
+        </is>
+      </c>
+      <c r="X15" t="n">
         <v>9</v>
       </c>
-      <c r="Y11" t="inlineStr">
+      <c r="Y15" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
+      <c r="Z15" t="inlineStr">
         <is>
           <t>010170</t>
         </is>

--- a/data/trending_integrated_20261012_10.xlsx
+++ b/data/trending_integrated_20261012_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z15"/>
+  <dimension ref="A1:Z16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,13 +578,13 @@
         <v>0.61</v>
       </c>
       <c r="E2" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F2" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G2" t="n">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="H2" t="n">
         <v>1.27</v>
@@ -610,7 +610,7 @@
         <v>0.66</v>
       </c>
       <c r="O2" t="n">
-        <v>19633786500</v>
+        <v>19669675340</v>
       </c>
       <c r="P2" t="n">
         <v>10300</v>
@@ -626,16 +626,16 @@
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>대장주로서 텐버거 확정 및 PHC파일 관련 수혜 기대감. 800조 사업 시작점 언급.</t>
+          <t>서산 대장 주장 및 텐버거 확정 기대. 외인 대량 매수 포착 및 관련주 언급.</t>
         </is>
       </c>
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>0.4</v>
+        <v>0.3</v>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>['PHC파일', '대장주', '수혜주']</t>
+          <t>['텐버거', '외인매수', '대장주']</t>
         </is>
       </c>
       <c r="X2" t="n">
@@ -655,31 +655,31 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>금호건설</t>
+          <t>금호전기</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13850</v>
+        <v>11070</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>'+24.33%</t>
+          <t>'+29.93%</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.64</v>
+        <v>0.91</v>
       </c>
       <c r="E3" t="n">
-        <v>59</v>
+        <v>40</v>
       </c>
       <c r="F3" t="n">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="G3" t="n">
-        <v>136</v>
+        <v>50</v>
       </c>
       <c r="H3" t="n">
-        <v>1.01</v>
+        <v>14.72</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>11140</v>
+        <v>8520</v>
       </c>
       <c r="K3" t="n">
-        <v>12000</v>
+        <v>9280</v>
       </c>
       <c r="L3" t="n">
-        <v>14100</v>
+        <v>11070</v>
       </c>
       <c r="M3" t="n">
-        <v>11710</v>
+        <v>9160</v>
       </c>
       <c r="N3" t="n">
-        <v>0.37</v>
+        <v>13.81</v>
       </c>
       <c r="O3" t="n">
-        <v>127216491200</v>
+        <v>126305452305</v>
       </c>
       <c r="P3" t="n">
-        <v>19380</v>
+        <v>14350</v>
       </c>
       <c r="Q3" t="n">
-        <v>3200</v>
+        <v>465</v>
       </c>
       <c r="R3" t="n">
-        <v>-414000</v>
+        <v>-102000</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>금호건설, 자체 개발 특허 출원 및 건설 확정으로 2차 상승 기대. 거래량 부진은 아쉬움.</t>
+          <t>매수 기조 유지 및 단기 차익 실현 의견 혼재. 재료와 흐름에 주목.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
@@ -727,7 +727,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['특허 출원', '건설 확정', '2차 상승']</t>
+          <t>['단기 차익', '재료']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -740,77 +740,77 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>002990</t>
+          <t>001210</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>강동씨앤엘</t>
+          <t>금호건설</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1649</v>
+        <v>13830</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+18.89%</t>
+          <t>'+24.15%</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.36</v>
+        <v>0.64</v>
       </c>
       <c r="E4" t="n">
-        <v>40</v>
+        <v>66</v>
       </c>
       <c r="F4" t="n">
-        <v>27</v>
+        <v>47</v>
       </c>
       <c r="G4" t="n">
-        <v>82</v>
+        <v>143</v>
       </c>
       <c r="H4" t="n">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J4" t="n">
-        <v>1387</v>
+        <v>11140</v>
       </c>
       <c r="K4" t="n">
-        <v>1450</v>
+        <v>12000</v>
       </c>
       <c r="L4" t="n">
-        <v>1710</v>
+        <v>14100</v>
       </c>
       <c r="M4" t="n">
-        <v>1436</v>
+        <v>11710</v>
       </c>
       <c r="N4" t="n">
-        <v>0.9</v>
+        <v>0.37</v>
       </c>
       <c r="O4" t="n">
-        <v>8966943630</v>
+        <v>131749599730</v>
       </c>
       <c r="P4" t="n">
-        <v>2930</v>
+        <v>19380</v>
       </c>
       <c r="Q4" t="n">
-        <v>910</v>
+        <v>3200</v>
       </c>
       <c r="R4" t="n">
-        <v>-108000</v>
+        <v>-414000</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>강동씨앤엘, 시멘트 수요 폭발 기대감 속 외국인 및 기관 매수세 유입. 대장주 역할 기대.</t>
+          <t>상승 기대감과 함께 자체 개발 특허 출원 언급. 거래량에 대한 의문 제기.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
@@ -819,7 +819,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['시멘트 수요', '외국인 매수', '대장주']</t>
+          <t>['특허 출원', '거래량', '기대감']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -832,38 +832,38 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>198440</t>
+          <t>002990</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>덕산넵코어스</t>
+          <t>강동씨앤엘</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15230</v>
+        <v>1660</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+9.49%</t>
+          <t>'+19.68%</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.12</v>
+        <v>0.36</v>
       </c>
       <c r="E5" t="n">
-        <v>136</v>
+        <v>41</v>
       </c>
       <c r="F5" t="n">
-        <v>65</v>
+        <v>26</v>
       </c>
       <c r="G5" t="n">
-        <v>149</v>
+        <v>88</v>
       </c>
       <c r="H5" t="n">
-        <v>0.21</v>
+        <v>1.26</v>
       </c>
       <c r="I5" t="inlineStr">
         <is>
@@ -871,51 +871,51 @@
         </is>
       </c>
       <c r="J5" t="n">
-        <v>13910</v>
+        <v>1387</v>
       </c>
       <c r="K5" t="n">
-        <v>13350</v>
+        <v>1450</v>
       </c>
       <c r="L5" t="n">
-        <v>15790</v>
+        <v>1710</v>
       </c>
       <c r="M5" t="n">
-        <v>13350</v>
+        <v>1436</v>
       </c>
       <c r="N5" t="n">
-        <v>0.09</v>
+        <v>0.9</v>
       </c>
       <c r="O5" t="n">
-        <v>79000055465</v>
+        <v>9172817838</v>
       </c>
       <c r="P5" t="n">
-        <v>28700</v>
+        <v>2930</v>
       </c>
       <c r="Q5" t="n">
-        <v>11600</v>
+        <v>910</v>
       </c>
       <c r="R5" t="n">
-        <v>85000</v>
+        <v>-108000</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>덕산넵코어스, 미국 방산주 팔란티어 상승에 따른 기대감. 상한가 및 17000원 돌파 기대.</t>
+          <t>매수 기조 유지 및 시멘트 수요 폭발 기대. 외국인 매도 압력 및 단일가 거래에 대한 언급.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['방산주', '팔란티어', '상한가']</t>
+          <t>['시멘트 수요', '외국인 매도', '단일가 거래']</t>
         </is>
       </c>
       <c r="X5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
@@ -924,38 +924,38 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>266690</t>
+          <t>198440</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>삼표시멘트</t>
+          <t>덕산넵코어스</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>7350</v>
+        <v>15010</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+3.81%</t>
+          <t>'+7.91%</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>-1.1</v>
+        <v>0.12</v>
       </c>
       <c r="E6" t="n">
-        <v>44</v>
+        <v>144</v>
       </c>
       <c r="F6" t="n">
-        <v>35</v>
+        <v>67</v>
       </c>
       <c r="G6" t="n">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="H6" t="n">
-        <v>1.99</v>
+        <v>0.21</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -963,38 +963,38 @@
         </is>
       </c>
       <c r="J6" t="n">
-        <v>7080</v>
+        <v>13910</v>
       </c>
       <c r="K6" t="n">
-        <v>6830</v>
+        <v>13350</v>
       </c>
       <c r="L6" t="n">
-        <v>7530</v>
+        <v>15790</v>
       </c>
       <c r="M6" t="n">
-        <v>6720</v>
+        <v>13350</v>
       </c>
       <c r="N6" t="n">
-        <v>3.09</v>
+        <v>0.09</v>
       </c>
       <c r="O6" t="n">
-        <v>29889724740</v>
+        <v>83864587175</v>
       </c>
       <c r="P6" t="n">
-        <v>23500</v>
+        <v>28700</v>
       </c>
       <c r="Q6" t="n">
-        <v>2890</v>
+        <v>11600</v>
       </c>
       <c r="R6" t="n">
-        <v>44000</v>
+        <v>85000</v>
       </c>
       <c r="S6" t="n">
         <v>0</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>삼표시멘트, 성수 메가프로젝트 및 건설 기초 소재 대장주로서의 입지 부각. 외국인 매수 증가 및 상가 기대.</t>
+          <t>덕산넵코어스, 미국 방산주 팔란티어 상승에 따른 기대감. 상한가 및 17000원 돌파 기대.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
@@ -1003,11 +1003,11 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['성수 메가프로젝트', '건설 기초 소재', '외국인 매수']</t>
+          <t>['방산주', '팔란티어', '상한가']</t>
         </is>
       </c>
       <c r="X6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -1016,90 +1016,90 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>038500</t>
+          <t>266690</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼표시멘트</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16370</v>
+        <v>7250</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'-1.80%</t>
+          <t>'+2.40%</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.01</v>
+        <v>-1.1</v>
       </c>
       <c r="E7" t="n">
-        <v>72</v>
+        <v>47</v>
       </c>
       <c r="F7" t="n">
-        <v>42</v>
+        <v>37</v>
       </c>
       <c r="G7" t="n">
-        <v>300</v>
+        <v>151</v>
       </c>
       <c r="H7" t="n">
-        <v>9.470000000000001</v>
+        <v>1.99</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>16670</v>
+        <v>7080</v>
       </c>
       <c r="K7" t="n">
-        <v>16500</v>
+        <v>6830</v>
       </c>
       <c r="L7" t="n">
-        <v>16870</v>
+        <v>7530</v>
       </c>
       <c r="M7" t="n">
-        <v>16240</v>
+        <v>6720</v>
       </c>
       <c r="N7" t="n">
-        <v>9.460000000000001</v>
+        <v>3.09</v>
       </c>
       <c r="O7" t="n">
-        <v>26939989870</v>
+        <v>33869968360</v>
       </c>
       <c r="P7" t="n">
-        <v>40350</v>
+        <v>23500</v>
       </c>
       <c r="Q7" t="n">
-        <v>3320</v>
+        <v>2890</v>
       </c>
       <c r="R7" t="n">
-        <v>221000</v>
+        <v>44000</v>
       </c>
       <c r="S7" t="n">
-        <v>11000</v>
+        <v>0</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>대우건설, 주주들의 적극적인 행동 촉구 및 범죄 척결 주장. 대차 해지, 뱅크런 관련 언급.</t>
+          <t>성수메가프로젝트 및 수도권 거점 공장 언급. 휴전 관련 및 외국인 매수 동향 주시.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0.2</v>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['소액주주연대', '범죄 척결', '대차 해지']</t>
+          <t>['성수메가프로젝트', '건설기초소재', '외국인 매수']</t>
         </is>
       </c>
       <c r="X7" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -1108,38 +1108,38 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>038500</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>255750</v>
+        <v>16390</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-2.39%</t>
+          <t>'-1.68%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>-0.03</v>
+        <v>0.01</v>
       </c>
       <c r="E8" t="n">
-        <v>800</v>
+        <v>77</v>
       </c>
       <c r="F8" t="n">
-        <v>484</v>
+        <v>43</v>
       </c>
       <c r="G8" t="n">
-        <v>1502</v>
+        <v>319</v>
       </c>
       <c r="H8" t="n">
-        <v>46.35</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -1147,38 +1147,38 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>262000</v>
+        <v>16670</v>
       </c>
       <c r="K8" t="n">
-        <v>260000</v>
+        <v>16500</v>
       </c>
       <c r="L8" t="n">
-        <v>262500</v>
+        <v>16870</v>
       </c>
       <c r="M8" t="n">
-        <v>254000</v>
+        <v>16240</v>
       </c>
       <c r="N8" t="n">
-        <v>46.38</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="O8" t="n">
-        <v>1351407489500</v>
+        <v>28232591475</v>
       </c>
       <c r="P8" t="n">
-        <v>374500</v>
+        <v>40350</v>
       </c>
       <c r="Q8" t="n">
-        <v>90200</v>
+        <v>3320</v>
       </c>
       <c r="R8" t="n">
-        <v>-171000</v>
+        <v>221000</v>
       </c>
       <c r="S8" t="n">
-        <v>90000</v>
+        <v>11000</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>삼성전자, 역대급 실적 발표 기대에도 불구하고 주가 하락세 지속. 국내 증시 및 정치 상황에 대한 불만 고조.</t>
+          <t>대차 해지와 뱅크런 관련 언급. 소액주주연대의 활동 촉구 및 범죄 행위 중단 요구.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
@@ -1187,7 +1187,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['역대급 실적', '국내 증시', '주가 하락']</t>
+          <t>['대차 해지', '뱅크런', '소액주주연대']</t>
         </is>
       </c>
       <c r="X8" t="n">
@@ -1200,90 +1200,90 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>44450</v>
+        <v>257250</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-2.63%</t>
+          <t>'-1.81%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.06</v>
+        <v>-0.03</v>
       </c>
       <c r="E9" t="n">
-        <v>298</v>
+        <v>800</v>
       </c>
       <c r="F9" t="n">
-        <v>193</v>
+        <v>487</v>
       </c>
       <c r="G9" t="n">
-        <v>1680</v>
+        <v>1499</v>
       </c>
       <c r="H9" t="n">
-        <v>13.33</v>
+        <v>46.35</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>45650</v>
+        <v>262000</v>
       </c>
       <c r="K9" t="n">
-        <v>47550</v>
+        <v>260000</v>
       </c>
       <c r="L9" t="n">
-        <v>47550</v>
+        <v>262500</v>
       </c>
       <c r="M9" t="n">
-        <v>43900</v>
+        <v>254000</v>
       </c>
       <c r="N9" t="n">
-        <v>13.39</v>
+        <v>46.38</v>
       </c>
       <c r="O9" t="n">
-        <v>27148532850</v>
+        <v>1441431761500</v>
       </c>
       <c r="P9" t="n">
-        <v>69200</v>
+        <v>374500</v>
       </c>
       <c r="Q9" t="n">
-        <v>24150</v>
+        <v>90200</v>
       </c>
       <c r="R9" t="n">
-        <v>-128000</v>
+        <v>-171000</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>90000</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>HLB 간암 1차 치료제 FDA 재승인 서류 제출, 리보세라닙/캄렐리주맙 병용요법 기대감.</t>
+          <t>낮은 영업이익과 주가 하락에 대한 불만 표출. 정치적 이슈와 연계된 부정적 전망.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.5</v>
+        <v>0.1</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['FDA', '리보세라닙', '간암']</t>
+          <t>['영업이익', '주가 하락', '정치적 이슈']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,38 +1292,38 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>삼기에너지솔루션즈</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2240</v>
+        <v>44800</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-2.82%</t>
+          <t>'-1.86%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.16</v>
+        <v>-0.06</v>
       </c>
       <c r="E10" t="n">
-        <v>55</v>
+        <v>311</v>
       </c>
       <c r="F10" t="n">
-        <v>27</v>
+        <v>200</v>
       </c>
       <c r="G10" t="n">
-        <v>58</v>
+        <v>1732</v>
       </c>
       <c r="H10" t="n">
-        <v>1.48</v>
+        <v>13.33</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -1331,51 +1331,51 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>2305</v>
+        <v>45650</v>
       </c>
       <c r="K10" t="n">
-        <v>2430</v>
+        <v>47550</v>
       </c>
       <c r="L10" t="n">
-        <v>2445</v>
+        <v>47550</v>
       </c>
       <c r="M10" t="n">
-        <v>2210</v>
+        <v>43900</v>
       </c>
       <c r="N10" t="n">
-        <v>1.32</v>
+        <v>13.39</v>
       </c>
       <c r="O10" t="n">
-        <v>26947652411</v>
+        <v>28268671750</v>
       </c>
       <c r="P10" t="n">
-        <v>2465</v>
+        <v>69200</v>
       </c>
       <c r="Q10" t="n">
-        <v>865</v>
+        <v>24150</v>
       </c>
       <c r="R10" t="n">
-        <v>-316000</v>
+        <v>-128000</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>삼기에너지솔루션즈, AI 데이터센터 확대에 따른 에너지 저장 장치 매출 급증 기대. 주가 상승 가능성 언급.</t>
+          <t>HLB 간암 1차 치료제 FDA 재승인 서류 제출, 리보세라닙/캄렐리주맙 병용요법 기대감.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.2</v>
+        <v>0.5</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['AI 데이터센터', '에너지 저장 장치', '매출 급증']</t>
+          <t>['FDA', '리보세라닙', '간암']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>419050</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7890</v>
+        <v>1636000</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-3.31%</t>
+          <t>'-2.68%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.01</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E11" t="n">
-        <v>79</v>
+        <v>800</v>
       </c>
       <c r="F11" t="n">
-        <v>55</v>
+        <v>479</v>
       </c>
       <c r="G11" t="n">
-        <v>351</v>
+        <v>1622</v>
       </c>
       <c r="H11" t="n">
-        <v>26.37</v>
+        <v>49.52</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,38 +1423,38 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>8160</v>
+        <v>1681000</v>
       </c>
       <c r="K11" t="n">
-        <v>8070</v>
+        <v>1640000</v>
       </c>
       <c r="L11" t="n">
-        <v>8110</v>
+        <v>1653000</v>
       </c>
       <c r="M11" t="n">
-        <v>7850</v>
+        <v>1605000</v>
       </c>
       <c r="N11" t="n">
-        <v>26.38</v>
+        <v>49.59</v>
       </c>
       <c r="O11" t="n">
-        <v>10128110160</v>
+        <v>1756535509500</v>
       </c>
       <c r="P11" t="n">
-        <v>17950</v>
+        <v>2987000</v>
       </c>
       <c r="Q11" t="n">
-        <v>7850</v>
+        <v>403000</v>
       </c>
       <c r="R11" t="n">
-        <v>-299000</v>
+        <v>-217000</v>
       </c>
       <c r="S11" t="n">
-        <v>-2000</v>
+        <v>44000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>LG디스플레이, 신기술(Flip)에 대한 회의적인 시각과 유상증자 가능성 제기. 주가 하락 및 폐악질이라는 비판.</t>
+          <t>정치적 이슈와 연관된 주가 하락 분석. 솔리다임 IPO 및 중복 상장 논란 언급.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
@@ -1463,11 +1463,11 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['Flip 기술', '유상증자', '주가 하락']</t>
+          <t>['정치테마', '솔리다임', '주가하락']</t>
         </is>
       </c>
       <c r="X11" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
@@ -1476,38 +1476,38 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1621000</v>
+        <v>18280</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-3.57%</t>
+          <t>'-3.08%</t>
         </is>
       </c>
       <c r="D12" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>800</v>
+        <v>87</v>
       </c>
       <c r="F12" t="n">
-        <v>481</v>
+        <v>50</v>
       </c>
       <c r="G12" t="n">
-        <v>1728</v>
+        <v>227</v>
       </c>
       <c r="H12" t="n">
-        <v>49.52</v>
+        <v>27.61</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
@@ -1515,51 +1515,51 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>1681000</v>
+        <v>18860</v>
       </c>
       <c r="K12" t="n">
-        <v>1640000</v>
+        <v>18690</v>
       </c>
       <c r="L12" t="n">
-        <v>1653000</v>
+        <v>18760</v>
       </c>
       <c r="M12" t="n">
-        <v>1605000</v>
+        <v>18100</v>
       </c>
       <c r="N12" t="n">
-        <v>49.59</v>
+        <v>27.68</v>
       </c>
       <c r="O12" t="n">
-        <v>1629287966500</v>
+        <v>23740080730</v>
       </c>
       <c r="P12" t="n">
-        <v>2987000</v>
+        <v>35350</v>
       </c>
       <c r="Q12" t="n">
-        <v>403000</v>
+        <v>18100</v>
       </c>
       <c r="R12" t="n">
-        <v>-217000</v>
+        <v>25000</v>
       </c>
       <c r="S12" t="n">
-        <v>44000</v>
+        <v>11000</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>정치적 이슈와 연계된 주가 하락 우려 및 배임 논란 제기. 최태원 회장 언급.</t>
+          <t>삼성중공업, LNG·FLNG 쌍끌이 수주 랠리에도 불구하고 주가 하락. 공매도 및 노조 문제 거론, 바닥 확인 필요.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['정치', '배임', '주가방어']</t>
+          <t>['LNG 수주', 'FLNG 수주', '공매도']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,90 +1568,90 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>삼기에너지솔루션즈</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18180</v>
+        <v>2230</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.61%</t>
+          <t>'-3.25%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.16</v>
       </c>
       <c r="E13" t="n">
-        <v>81</v>
+        <v>58</v>
       </c>
       <c r="F13" t="n">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="G13" t="n">
-        <v>223</v>
+        <v>61</v>
       </c>
       <c r="H13" t="n">
-        <v>27.61</v>
+        <v>1.48</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>18860</v>
+        <v>2305</v>
       </c>
       <c r="K13" t="n">
-        <v>18690</v>
+        <v>2430</v>
       </c>
       <c r="L13" t="n">
-        <v>18760</v>
+        <v>2445</v>
       </c>
       <c r="M13" t="n">
-        <v>18100</v>
+        <v>2210</v>
       </c>
       <c r="N13" t="n">
-        <v>27.68</v>
+        <v>1.32</v>
       </c>
       <c r="O13" t="n">
-        <v>22834299415</v>
+        <v>27235393664</v>
       </c>
       <c r="P13" t="n">
-        <v>35350</v>
+        <v>2465</v>
       </c>
       <c r="Q13" t="n">
-        <v>18100</v>
+        <v>865</v>
       </c>
       <c r="R13" t="n">
-        <v>25000</v>
+        <v>-316000</v>
       </c>
       <c r="S13" t="n">
-        <v>11000</v>
+        <v>0</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>삼성중공업, LNG·FLNG 쌍끌이 수주 랠리에도 불구하고 주가 하락. 공매도 및 노조 문제 거론, 바닥 확인 필요.</t>
+          <t>대표에 대한 부정적 언급과 함께 인공지능 데이터센터 확대에 따른 매출 증대 기대.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['LNG 수주', 'FLNG 수주', '공매도']</t>
+          <t>['인공지능', '매출 증대', '대표']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,38 +1660,38 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>419050</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>26250</v>
+        <v>7890</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-6.58%</t>
+          <t>'-3.31%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.01</v>
       </c>
       <c r="E14" t="n">
-        <v>41</v>
+        <v>82</v>
       </c>
       <c r="F14" t="n">
-        <v>30</v>
+        <v>57</v>
       </c>
       <c r="G14" t="n">
-        <v>42</v>
+        <v>360</v>
       </c>
       <c r="H14" t="n">
-        <v>9.460000000000001</v>
+        <v>26.37</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -1699,38 +1699,38 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>28100</v>
+        <v>8160</v>
       </c>
       <c r="K14" t="n">
-        <v>27600</v>
+        <v>8070</v>
       </c>
       <c r="L14" t="n">
-        <v>27800</v>
+        <v>8110</v>
       </c>
       <c r="M14" t="n">
-        <v>26050</v>
+        <v>7850</v>
       </c>
       <c r="N14" t="n">
-        <v>10.02</v>
+        <v>26.38</v>
       </c>
       <c r="O14" t="n">
-        <v>32423993125</v>
+        <v>10512956125</v>
       </c>
       <c r="P14" t="n">
-        <v>75900</v>
+        <v>17950</v>
       </c>
       <c r="Q14" t="n">
-        <v>15960</v>
+        <v>7850</v>
       </c>
       <c r="R14" t="n">
-        <v>-24000</v>
+        <v>-299000</v>
       </c>
       <c r="S14" t="n">
-        <v>2000</v>
+        <v>-2000</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>대한전선, 경영진 비판 및 실적 부진에 대한 실망감 표출. 하한가 예상 및 잡주라는 부정적 평가.</t>
+          <t>주가 하락과 악재 뉴스에 대한 불만. FLiPP 기술 상용화 및 유상증자 가능성에 대한 부정적 전망.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
@@ -1739,11 +1739,11 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['경영진 비판', '실적 부진', '하한가']</t>
+          <t>['주가 하락', 'FLiPP', '유상증자']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,7 +1752,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>001440</t>
+          <t>034220</t>
         </is>
       </c>
     </row>
@@ -1763,24 +1763,24 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15840</v>
+        <v>15980</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-6.66%</t>
+          <t>'-5.83%</t>
         </is>
       </c>
       <c r="D15" t="n">
         <v>-0.6</v>
       </c>
       <c r="E15" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="F15" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="G15" t="n">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="H15" t="n">
         <v>3.37</v>
@@ -1806,7 +1806,7 @@
         <v>3.97</v>
       </c>
       <c r="O15" t="n">
-        <v>54752297030</v>
+        <v>57016185685</v>
       </c>
       <c r="P15" t="n">
         <v>31500</v>
@@ -1822,7 +1822,7 @@
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>AI 관련 광통신 테마 상승 기대감과 공매도 규제 및 지수 하락 이슈 혼재. 10월 3만원 예상.</t>
+          <t>광통신 시장 성장률 및 AI 관련 긍정적 전망 속 주가 하락 및 공매도 규제에 대한 불만.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
@@ -1831,7 +1831,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['광통신', 'AI', '테마']</t>
+          <t>['광통신', 'AI', '공매도']</t>
         </is>
       </c>
       <c r="X15" t="n">
@@ -1845,6 +1845,98 @@
       <c r="Z15" t="inlineStr">
         <is>
           <t>010170</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>대한전선</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>26350</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>'-6.23%</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="E16" t="n">
+        <v>44</v>
+      </c>
+      <c r="F16" t="n">
+        <v>32</v>
+      </c>
+      <c r="G16" t="n">
+        <v>44</v>
+      </c>
+      <c r="H16" t="n">
+        <v>9.460000000000001</v>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J16" t="n">
+        <v>28100</v>
+      </c>
+      <c r="K16" t="n">
+        <v>27600</v>
+      </c>
+      <c r="L16" t="n">
+        <v>27800</v>
+      </c>
+      <c r="M16" t="n">
+        <v>26050</v>
+      </c>
+      <c r="N16" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="O16" t="n">
+        <v>34026377525</v>
+      </c>
+      <c r="P16" t="n">
+        <v>75900</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>15960</v>
+      </c>
+      <c r="R16" t="n">
+        <v>-24000</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2000</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>경영진에 대한 비판과 주가 폭락에 대한 우려. 실적 부진 및 LS 기술 유출 영향 언급.</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>['경영진 비판', '주가 폭락', '실적 부진']</t>
+        </is>
+      </c>
+      <c r="X16" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>001440</t>
         </is>
       </c>
     </row>

--- a/data/trending_integrated_20261012_10.xlsx
+++ b/data/trending_integrated_20261012_10.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z16"/>
+  <dimension ref="A1:Z18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,13 +578,13 @@
         <v>0.61</v>
       </c>
       <c r="E2" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F2" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G2" t="n">
-        <v>115</v>
+        <v>121</v>
       </c>
       <c r="H2" t="n">
         <v>1.27</v>
@@ -610,7 +610,7 @@
         <v>0.66</v>
       </c>
       <c r="O2" t="n">
-        <v>19669675340</v>
+        <v>19695194340</v>
       </c>
       <c r="P2" t="n">
         <v>10300</v>
@@ -670,13 +670,13 @@
         <v>0.91</v>
       </c>
       <c r="E3" t="n">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F3" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="G3" t="n">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="H3" t="n">
         <v>14.72</v>
@@ -702,7 +702,7 @@
         <v>13.81</v>
       </c>
       <c r="O3" t="n">
-        <v>126305452305</v>
+        <v>126507778695</v>
       </c>
       <c r="P3" t="n">
         <v>14350</v>
@@ -718,16 +718,16 @@
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>매수 기조 유지 및 단기 차익 실현 의견 혼재. 재료와 흐름에 주목.</t>
+          <t>단기 급등세 연출, 재료 및 수급 동시 긍정적 전망. 그러나 명확한 공시 기반 근거 부족.</t>
         </is>
       </c>
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>['단기 차익', '재료']</t>
+          <t>['단기 급등', '재료', '수급']</t>
         </is>
       </c>
       <c r="X3" t="n">
@@ -751,24 +751,24 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13830</v>
+        <v>13780</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>'+24.15%</t>
+          <t>'+23.70%</t>
         </is>
       </c>
       <c r="D4" t="n">
         <v>0.64</v>
       </c>
       <c r="E4" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="F4" t="n">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G4" t="n">
-        <v>143</v>
+        <v>154</v>
       </c>
       <c r="H4" t="n">
         <v>1.01</v>
@@ -794,7 +794,7 @@
         <v>0.37</v>
       </c>
       <c r="O4" t="n">
-        <v>131749599730</v>
+        <v>134155361925</v>
       </c>
       <c r="P4" t="n">
         <v>19380</v>
@@ -810,16 +810,16 @@
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>상승 기대감과 함께 자체 개발 특허 출원 언급. 거래량에 대한 의문 제기.</t>
+          <t>자체 개발 특허 출원 발표, 긍정적 기대감 형성. 거래량 동반 상승세 지속 여부 관건.</t>
         </is>
       </c>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>['특허 출원', '거래량', '기대감']</t>
+          <t>['특허 출원', '거래량', '상승세']</t>
         </is>
       </c>
       <c r="X4" t="n">
@@ -843,24 +843,24 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1660</v>
+        <v>1632</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>'+19.68%</t>
+          <t>'+17.66%</t>
         </is>
       </c>
       <c r="D5" t="n">
         <v>0.36</v>
       </c>
       <c r="E5" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="G5" t="n">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H5" t="n">
         <v>1.26</v>
@@ -886,7 +886,7 @@
         <v>0.9</v>
       </c>
       <c r="O5" t="n">
-        <v>9172817838</v>
+        <v>9353775115</v>
       </c>
       <c r="P5" t="n">
         <v>2930</v>
@@ -902,16 +902,16 @@
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>매수 기조 유지 및 시멘트 수요 폭발 기대. 외국인 매도 압력 및 단일가 거래에 대한 언급.</t>
+          <t>호남 반도체 관련 수혜주 언급, 시멘트 수요 폭발 기대. 외국인 및 기관 매도 압력 속 단기 시세 분출 가능성.</t>
         </is>
       </c>
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>['시멘트 수요', '외국인 매도', '단일가 거래']</t>
+          <t>['호남반도체', '시멘트', '수요 폭발']</t>
         </is>
       </c>
       <c r="X5" t="n">
@@ -935,24 +935,24 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15010</v>
+        <v>14910</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>'+7.91%</t>
+          <t>'+7.19%</t>
         </is>
       </c>
       <c r="D6" t="n">
         <v>0.12</v>
       </c>
       <c r="E6" t="n">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="F6" t="n">
         <v>67</v>
       </c>
       <c r="G6" t="n">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="H6" t="n">
         <v>0.21</v>
@@ -978,7 +978,7 @@
         <v>0.09</v>
       </c>
       <c r="O6" t="n">
-        <v>83864587175</v>
+        <v>88237440725</v>
       </c>
       <c r="P6" t="n">
         <v>28700</v>
@@ -994,16 +994,16 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>덕산넵코어스, 미국 방산주 팔란티어 상승에 따른 기대감. 상한가 및 17000원 돌파 기대.</t>
+          <t>미국 방산주 동반 강세, 전쟁 긴장감 고조 수혜 기대. 보호예수 해제 및 주가 변동성 주의.</t>
         </is>
       </c>
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="n">
-        <v>0.3</v>
+        <v>0.4</v>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>['방산주', '팔란티어', '상한가']</t>
+          <t>['방산 테마', '전쟁 긴장감', '보호예수']</t>
         </is>
       </c>
       <c r="X6" t="n">
@@ -1027,24 +1027,24 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>7250</v>
+        <v>7390</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>'+2.40%</t>
+          <t>'+4.38%</t>
         </is>
       </c>
       <c r="D7" t="n">
         <v>-1.1</v>
       </c>
       <c r="E7" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F7" t="n">
         <v>37</v>
       </c>
       <c r="G7" t="n">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="H7" t="n">
         <v>1.99</v>
@@ -1070,7 +1070,7 @@
         <v>3.09</v>
       </c>
       <c r="O7" t="n">
-        <v>33869968360</v>
+        <v>36268085685</v>
       </c>
       <c r="P7" t="n">
         <v>23500</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>성수메가프로젝트 및 수도권 거점 공장 언급. 휴전 관련 및 외국인 매수 동향 주시.</t>
+          <t>부동산 테마주로서 수도권 거점 공장을 보유하며, 10월 12일 성수 메가 프로젝트와 연관된 기대감이 있으나, 일부 매도 물량과 AI 관련 부정적 전망도 존재.</t>
         </is>
       </c>
       <c r="U7" t="inlineStr"/>
@@ -1095,7 +1095,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>['성수메가프로젝트', '건설기초소재', '외국인 매수']</t>
+          <t>['부동산 테마주', '거점 공장', 'AI 전망']</t>
         </is>
       </c>
       <c r="X7" t="n">
@@ -1115,83 +1115,83 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>글로벌테크놀로지</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16390</v>
+        <v>11640</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>'-1.68%</t>
+          <t>'+2.65%</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="E8" t="n">
-        <v>77</v>
+        <v>40</v>
       </c>
       <c r="F8" t="n">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="G8" t="n">
-        <v>319</v>
+        <v>45</v>
       </c>
       <c r="H8" t="n">
-        <v>9.470000000000001</v>
+        <v>0.41</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J8" t="n">
-        <v>16670</v>
+        <v>11340</v>
       </c>
       <c r="K8" t="n">
-        <v>16500</v>
+        <v>11340</v>
       </c>
       <c r="L8" t="n">
-        <v>16870</v>
+        <v>12470</v>
       </c>
       <c r="M8" t="n">
-        <v>16240</v>
+        <v>11120</v>
       </c>
       <c r="N8" t="n">
-        <v>9.460000000000001</v>
+        <v>0.44</v>
       </c>
       <c r="O8" t="n">
-        <v>28232591475</v>
+        <v>23064129160</v>
       </c>
       <c r="P8" t="n">
-        <v>40350</v>
+        <v>29750</v>
       </c>
       <c r="Q8" t="n">
-        <v>3320</v>
+        <v>11120</v>
       </c>
       <c r="R8" t="n">
-        <v>221000</v>
+        <v>56000</v>
       </c>
       <c r="S8" t="n">
-        <v>11000</v>
+        <v>0</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>대차 해지와 뱅크런 관련 언급. 소액주주연대의 활동 촉구 및 범죄 행위 중단 요구.</t>
+          <t>AI 데이터센터 광통신 영역 확장 및 성호전자와 CPO 광정렬 장비용 자외선 경화 광원 개발 추진 뉴스가 있으나, 보호예수 해제 및 부정적 의견도 공존.</t>
         </is>
       </c>
       <c r="U8" t="inlineStr"/>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.4</v>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>['대차 해지', '뱅크런', '소액주주연대']</t>
+          <t>['AI 데이터센터', '광통신', '보호예수 해제']</t>
         </is>
       </c>
       <c r="X8" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
@@ -1200,38 +1200,38 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>047040</t>
+          <t>486510</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>국제약품</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>257250</v>
+        <v>4205</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>'-1.81%</t>
+          <t>'-1.52%</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>-0.03</v>
+        <v>-2.94</v>
       </c>
       <c r="E9" t="n">
-        <v>800</v>
+        <v>41</v>
       </c>
       <c r="F9" t="n">
-        <v>487</v>
+        <v>25</v>
       </c>
       <c r="G9" t="n">
-        <v>1499</v>
+        <v>54</v>
       </c>
       <c r="H9" t="n">
-        <v>46.35</v>
+        <v>1.52</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -1239,51 +1239,51 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>262000</v>
+        <v>4270</v>
       </c>
       <c r="K9" t="n">
-        <v>260000</v>
+        <v>4150</v>
       </c>
       <c r="L9" t="n">
-        <v>262500</v>
+        <v>4495</v>
       </c>
       <c r="M9" t="n">
-        <v>254000</v>
+        <v>4090</v>
       </c>
       <c r="N9" t="n">
-        <v>46.38</v>
+        <v>4.46</v>
       </c>
       <c r="O9" t="n">
-        <v>1441431761500</v>
+        <v>14288807281</v>
       </c>
       <c r="P9" t="n">
-        <v>374500</v>
+        <v>5470</v>
       </c>
       <c r="Q9" t="n">
-        <v>90200</v>
+        <v>2810</v>
       </c>
       <c r="R9" t="n">
-        <v>-171000</v>
+        <v>-35000</v>
       </c>
       <c r="S9" t="n">
-        <v>90000</v>
+        <v>0</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>낮은 영업이익과 주가 하락에 대한 불만 표출. 정치적 이슈와 연계된 부정적 전망.</t>
+          <t>러시아 코로나 관련 뉴스 언급, 모더나 급등 영향 분석. 명확한 모멘텀 부재 속 단기적 기대감.</t>
         </is>
       </c>
       <c r="U9" t="inlineStr"/>
       <c r="V9" t="n">
-        <v>0.1</v>
+        <v>0.5</v>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>['영업이익', '주가 하락', '정치적 이슈']</t>
+          <t>['코로나19', '모더나', '단기 모멘텀']</t>
         </is>
       </c>
       <c r="X9" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
@@ -1292,90 +1292,90 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>002720</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HLB</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>44800</v>
+        <v>257500</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>'-1.86%</t>
+          <t>'-1.72%</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>-0.06</v>
+        <v>-0.03</v>
       </c>
       <c r="E10" t="n">
-        <v>311</v>
+        <v>800</v>
       </c>
       <c r="F10" t="n">
-        <v>200</v>
+        <v>484</v>
       </c>
       <c r="G10" t="n">
-        <v>1732</v>
+        <v>1500</v>
       </c>
       <c r="H10" t="n">
-        <v>13.33</v>
+        <v>46.35</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J10" t="n">
-        <v>45650</v>
+        <v>262000</v>
       </c>
       <c r="K10" t="n">
-        <v>47550</v>
+        <v>260000</v>
       </c>
       <c r="L10" t="n">
-        <v>47550</v>
+        <v>262500</v>
       </c>
       <c r="M10" t="n">
-        <v>43900</v>
+        <v>254000</v>
       </c>
       <c r="N10" t="n">
-        <v>13.39</v>
+        <v>46.38</v>
       </c>
       <c r="O10" t="n">
-        <v>28268671750</v>
+        <v>1541566519000</v>
       </c>
       <c r="P10" t="n">
-        <v>69200</v>
+        <v>374500</v>
       </c>
       <c r="Q10" t="n">
-        <v>24150</v>
+        <v>90200</v>
       </c>
       <c r="R10" t="n">
-        <v>-128000</v>
+        <v>-171000</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>90000</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>HLB 간암 1차 치료제 FDA 재승인 서류 제출, 리보세라닙/캄렐리주맙 병용요법 기대감.</t>
+          <t>역대급 실적 기대에도 불구하고 주가 부양 실패, 정치적 이슈와 노조 문제로 인한 부정적 심리 확산.</t>
         </is>
       </c>
       <c r="U10" t="inlineStr"/>
       <c r="V10" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>['FDA', '리보세라닙', '간암']</t>
+          <t>['실적 부진', '정치적 이슈', '노조']</t>
         </is>
       </c>
       <c r="X10" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
@@ -1384,38 +1384,38 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>028300</t>
+          <t>005930</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1636000</v>
+        <v>16360</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>'-2.68%</t>
+          <t>'-1.86%</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>-0.07000000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="E11" t="n">
-        <v>800</v>
+        <v>84</v>
       </c>
       <c r="F11" t="n">
-        <v>479</v>
+        <v>43</v>
       </c>
       <c r="G11" t="n">
-        <v>1622</v>
+        <v>337</v>
       </c>
       <c r="H11" t="n">
-        <v>49.52</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
@@ -1423,47 +1423,47 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>1681000</v>
+        <v>16670</v>
       </c>
       <c r="K11" t="n">
-        <v>1640000</v>
+        <v>16500</v>
       </c>
       <c r="L11" t="n">
-        <v>1653000</v>
+        <v>16870</v>
       </c>
       <c r="M11" t="n">
-        <v>1605000</v>
+        <v>16240</v>
       </c>
       <c r="N11" t="n">
-        <v>49.59</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="O11" t="n">
-        <v>1756535509500</v>
+        <v>29530588480</v>
       </c>
       <c r="P11" t="n">
-        <v>2987000</v>
+        <v>40350</v>
       </c>
       <c r="Q11" t="n">
-        <v>403000</v>
+        <v>3320</v>
       </c>
       <c r="R11" t="n">
-        <v>-217000</v>
+        <v>221000</v>
       </c>
       <c r="S11" t="n">
-        <v>44000</v>
+        <v>11000</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>정치적 이슈와 연관된 주가 하락 분석. 솔리다임 IPO 및 중복 상장 논란 언급.</t>
+          <t>대차 해지와 뱅크런 관련 언급. 소액주주연대의 활동 촉구 및 범죄 행위 중단 요구.</t>
         </is>
       </c>
       <c r="U11" t="inlineStr"/>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>['정치테마', '솔리다임', '주가하락']</t>
+          <t>['대차 해지', '뱅크런', '소액주주연대']</t>
         </is>
       </c>
       <c r="X11" t="n">
@@ -1476,90 +1476,90 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>047040</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>HLB</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18280</v>
+        <v>44750</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>'-3.08%</t>
+          <t>'-1.97%</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="E12" t="n">
-        <v>87</v>
+        <v>318</v>
       </c>
       <c r="F12" t="n">
-        <v>50</v>
+        <v>201</v>
       </c>
       <c r="G12" t="n">
-        <v>227</v>
+        <v>1815</v>
       </c>
       <c r="H12" t="n">
-        <v>27.61</v>
+        <v>13.33</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>18860</v>
+        <v>45650</v>
       </c>
       <c r="K12" t="n">
-        <v>18690</v>
+        <v>47550</v>
       </c>
       <c r="L12" t="n">
-        <v>18760</v>
+        <v>47550</v>
       </c>
       <c r="M12" t="n">
-        <v>18100</v>
+        <v>43900</v>
       </c>
       <c r="N12" t="n">
-        <v>27.68</v>
+        <v>13.39</v>
       </c>
       <c r="O12" t="n">
-        <v>23740080730</v>
+        <v>28990928150</v>
       </c>
       <c r="P12" t="n">
-        <v>35350</v>
+        <v>69200</v>
       </c>
       <c r="Q12" t="n">
-        <v>18100</v>
+        <v>24150</v>
       </c>
       <c r="R12" t="n">
-        <v>25000</v>
+        <v>-128000</v>
       </c>
       <c r="S12" t="n">
-        <v>11000</v>
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
-          <t>삼성중공업, LNG·FLNG 쌍끌이 수주 랠리에도 불구하고 주가 하락. 공매도 및 노조 문제 거론, 바닥 확인 필요.</t>
+          <t>FDA에 리보세라닙, 캄렐리주맙 병용요법 간암 1차 치료제 재승인 서류를 제출했다는 공시가 핵심이며, 이에 따른 긍정적인 기대감과 함께 기관의 매수세 유입을 촉구하는 의견이 다수.</t>
         </is>
       </c>
       <c r="U12" t="inlineStr"/>
       <c r="V12" t="n">
-        <v>0.3</v>
+        <v>0.6</v>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>['LNG 수주', 'FLNG 수주', '공매도']</t>
+          <t>['FDA 재승인', '리보세라닙', '캄렐리주맙']</t>
         </is>
       </c>
       <c r="X12" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
@@ -1568,90 +1568,90 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>028300</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>삼기에너지솔루션즈</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2230</v>
+        <v>1635000</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>'-3.25%</t>
+          <t>'-2.74%</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.16</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E13" t="n">
-        <v>58</v>
+        <v>800</v>
       </c>
       <c r="F13" t="n">
-        <v>28</v>
+        <v>477</v>
       </c>
       <c r="G13" t="n">
-        <v>61</v>
+        <v>1576</v>
       </c>
       <c r="H13" t="n">
-        <v>1.48</v>
+        <v>49.52</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J13" t="n">
-        <v>2305</v>
+        <v>1681000</v>
       </c>
       <c r="K13" t="n">
-        <v>2430</v>
+        <v>1640000</v>
       </c>
       <c r="L13" t="n">
-        <v>2445</v>
+        <v>1653000</v>
       </c>
       <c r="M13" t="n">
-        <v>2210</v>
+        <v>1605000</v>
       </c>
       <c r="N13" t="n">
-        <v>1.32</v>
+        <v>49.59</v>
       </c>
       <c r="O13" t="n">
-        <v>27235393664</v>
+        <v>1923256937000</v>
       </c>
       <c r="P13" t="n">
-        <v>2465</v>
+        <v>2987000</v>
       </c>
       <c r="Q13" t="n">
-        <v>865</v>
+        <v>403000</v>
       </c>
       <c r="R13" t="n">
-        <v>-316000</v>
+        <v>-217000</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>44000</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>대표에 대한 부정적 언급과 함께 인공지능 데이터센터 확대에 따른 매출 증대 기대.</t>
+          <t>정치적 요인과 관련된 부정적 언급이 많으며, 주가 하락에 대한 불만이 제기되고 있고, 자사주 매입 종료 시점과 중복 상장 논란이 주가 하락의 요인으로 지적됨.</t>
         </is>
       </c>
       <c r="U13" t="inlineStr"/>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>['인공지능', '매출 증대', '대표']</t>
+          <t>['정치적 요인', '중복 상장', '주가 하락']</t>
         </is>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
@@ -1660,90 +1660,90 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>419050</t>
+          <t>000660</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>LG디스플레이</t>
+          <t>삼기에너지솔루션즈</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7890</v>
+        <v>2235</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>'-3.31%</t>
+          <t>'-3.04%</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>-0.01</v>
+        <v>0.16</v>
       </c>
       <c r="E14" t="n">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="F14" t="n">
-        <v>57</v>
+        <v>31</v>
       </c>
       <c r="G14" t="n">
-        <v>360</v>
+        <v>64</v>
       </c>
       <c r="H14" t="n">
-        <v>26.37</v>
+        <v>1.48</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MarketType.KOSPI</t>
+          <t>MarketType.KOSDAQ</t>
         </is>
       </c>
       <c r="J14" t="n">
-        <v>8160</v>
+        <v>2305</v>
       </c>
       <c r="K14" t="n">
-        <v>8070</v>
+        <v>2430</v>
       </c>
       <c r="L14" t="n">
-        <v>8110</v>
+        <v>2445</v>
       </c>
       <c r="M14" t="n">
-        <v>7850</v>
+        <v>2210</v>
       </c>
       <c r="N14" t="n">
-        <v>26.38</v>
+        <v>1.32</v>
       </c>
       <c r="O14" t="n">
-        <v>10512956125</v>
+        <v>27429823784</v>
       </c>
       <c r="P14" t="n">
-        <v>17950</v>
+        <v>2465</v>
       </c>
       <c r="Q14" t="n">
-        <v>7850</v>
+        <v>865</v>
       </c>
       <c r="R14" t="n">
-        <v>-299000</v>
+        <v>-316000</v>
       </c>
       <c r="S14" t="n">
-        <v>-2000</v>
+        <v>0</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>주가 하락과 악재 뉴스에 대한 불만. FLiPP 기술 상용화 및 유상증자 가능성에 대한 부정적 전망.</t>
+          <t>인공지능 데이터센터 확대 따른 에너지저장장치용 유연회로기판 매출 급증 기대. 단기 급등 후 차익실현 압력.</t>
         </is>
       </c>
       <c r="U14" t="inlineStr"/>
       <c r="V14" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>['주가 하락', 'FLiPP', '유상증자']</t>
+          <t>['AI 데이터센터', 'ESS', '유연회로기판']</t>
         </is>
       </c>
       <c r="X14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y14" t="inlineStr">
         <is>
@@ -1752,90 +1752,90 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>034220</t>
+          <t>419050</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>대한광통신</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15980</v>
+        <v>18250</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>'-5.83%</t>
+          <t>'-3.23%</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>-0.6</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E15" t="n">
-        <v>106</v>
+        <v>88</v>
       </c>
       <c r="F15" t="n">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="G15" t="n">
-        <v>349</v>
+        <v>232</v>
       </c>
       <c r="H15" t="n">
-        <v>3.37</v>
+        <v>27.61</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MarketType.KOSDAQ</t>
+          <t>MarketType.KOSPI</t>
         </is>
       </c>
       <c r="J15" t="n">
-        <v>16970</v>
+        <v>18860</v>
       </c>
       <c r="K15" t="n">
-        <v>17030</v>
+        <v>18690</v>
       </c>
       <c r="L15" t="n">
-        <v>17400</v>
+        <v>18760</v>
       </c>
       <c r="M15" t="n">
-        <v>15650</v>
+        <v>18100</v>
       </c>
       <c r="N15" t="n">
-        <v>3.97</v>
+        <v>27.68</v>
       </c>
       <c r="O15" t="n">
-        <v>57016185685</v>
+        <v>24830780160</v>
       </c>
       <c r="P15" t="n">
-        <v>31500</v>
+        <v>35350</v>
       </c>
       <c r="Q15" t="n">
-        <v>1272</v>
+        <v>18100</v>
       </c>
       <c r="R15" t="n">
-        <v>-29000</v>
+        <v>25000</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>11000</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
-          <t>광통신 시장 성장률 및 AI 관련 긍정적 전망 속 주가 하락 및 공매도 규제에 대한 불만.</t>
+          <t>LNG·FLNG 쌍끌이 수주 랠리 긍정적, 그러나 공매도 및 노조 이슈로 인한 주가 하락 압력 지속.</t>
         </is>
       </c>
       <c r="U15" t="inlineStr"/>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>['광통신', 'AI', '공매도']</t>
+          <t>['수주 랠리', '공매도', '노조 이슈']</t>
         </is>
       </c>
       <c r="X15" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
@@ -1844,38 +1844,38 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>010170</t>
+          <t>010140</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>대한전선</t>
+          <t>LG디스플레이</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>26350</v>
+        <v>7840</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>'-6.23%</t>
+          <t>'-3.92%</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.01</v>
       </c>
       <c r="E16" t="n">
-        <v>44</v>
+        <v>85</v>
       </c>
       <c r="F16" t="n">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="G16" t="n">
-        <v>44</v>
+        <v>400</v>
       </c>
       <c r="H16" t="n">
-        <v>9.460000000000001</v>
+        <v>26.37</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1883,58 +1883,242 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>28100</v>
+        <v>8160</v>
       </c>
       <c r="K16" t="n">
-        <v>27600</v>
+        <v>8070</v>
       </c>
       <c r="L16" t="n">
-        <v>27800</v>
+        <v>8110</v>
       </c>
       <c r="M16" t="n">
-        <v>26050</v>
+        <v>7830</v>
       </c>
       <c r="N16" t="n">
-        <v>10.02</v>
+        <v>26.38</v>
       </c>
       <c r="O16" t="n">
-        <v>34026377525</v>
+        <v>11651272760</v>
       </c>
       <c r="P16" t="n">
-        <v>75900</v>
+        <v>17950</v>
       </c>
       <c r="Q16" t="n">
-        <v>15960</v>
+        <v>7830</v>
       </c>
       <c r="R16" t="n">
-        <v>-24000</v>
+        <v>-299000</v>
       </c>
       <c r="S16" t="n">
-        <v>2000</v>
+        <v>-2000</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
-          <t>경영진에 대한 비판과 주가 폭락에 대한 우려. 실적 부진 및 LS 기술 유출 영향 언급.</t>
+          <t>악의적 공시 및 주가 조작 의혹 제기, 유상증자 가능성 언급. 재무적 불확실성 및 주주 불만 고조.</t>
         </is>
       </c>
       <c r="U16" t="inlineStr"/>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>['경영진 비판', '주가 폭락', '실적 부진']</t>
+          <t>['주가 조작', '유상증자', '재무 불확실성']</t>
         </is>
       </c>
       <c r="X16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>034220</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>대한광통신</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>15970</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>'-5.89%</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="E17" t="n">
+        <v>106</v>
+      </c>
+      <c r="F17" t="n">
+        <v>55</v>
+      </c>
+      <c r="G17" t="n">
+        <v>357</v>
+      </c>
+      <c r="H17" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>MarketType.KOSDAQ</t>
+        </is>
+      </c>
+      <c r="J17" t="n">
+        <v>16970</v>
+      </c>
+      <c r="K17" t="n">
+        <v>17030</v>
+      </c>
+      <c r="L17" t="n">
+        <v>17400</v>
+      </c>
+      <c r="M17" t="n">
+        <v>15650</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3.97</v>
+      </c>
+      <c r="O17" t="n">
+        <v>58748661680</v>
+      </c>
+      <c r="P17" t="n">
+        <v>31500</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>1272</v>
+      </c>
+      <c r="R17" t="n">
+        <v>-29000</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>광통신 테마로 10월 3만원 예상 등 긍정적 전망이 있으나, 연휴 속보 및 AI 관련 긍정 뉴스가 있지만, 3일간 20% 하락과 중요 지지선 이탈 등 부정적 신호가 강함.</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>['광통신 테마', '지지선 이탈', '급상승 기대']</t>
+        </is>
+      </c>
+      <c r="X17" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>활성</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>010170</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>대한전선</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>26400</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>'-6.05%</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="E18" t="n">
+        <v>48</v>
+      </c>
+      <c r="F18" t="n">
+        <v>35</v>
+      </c>
+      <c r="G18" t="n">
+        <v>50</v>
+      </c>
+      <c r="H18" t="n">
+        <v>9.460000000000001</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>MarketType.KOSPI</t>
+        </is>
+      </c>
+      <c r="J18" t="n">
+        <v>28100</v>
+      </c>
+      <c r="K18" t="n">
+        <v>27600</v>
+      </c>
+      <c r="L18" t="n">
+        <v>27800</v>
+      </c>
+      <c r="M18" t="n">
+        <v>26050</v>
+      </c>
+      <c r="N18" t="n">
+        <v>10.02</v>
+      </c>
+      <c r="O18" t="n">
+        <v>35503290525</v>
+      </c>
+      <c r="P18" t="n">
+        <v>75900</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>15960</v>
+      </c>
+      <c r="R18" t="n">
+        <v>-24000</v>
+      </c>
+      <c r="S18" t="n">
+        <v>2000</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>경영진의 무능력 지적, LS 기술유출 타격 언급. 실적 개선 근거 부족 및 투매 우려.</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>['경영진 부진', '기술유출', '실적 우려']</t>
+        </is>
+      </c>
+      <c r="X18" t="n">
         <v>3</v>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Y18" t="inlineStr">
         <is>
           <t>활성</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
+      <c r="Z18" t="inlineStr">
         <is>
           <t>001440</t>
         </is>
